--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -656,77 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>31426100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>18028600</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -734,14 +733,14 @@
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>38418800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>18476200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>41334900</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -752,8 +751,11 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -763,20 +765,20 @@
       <c r="E9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="F9" s="3">
+        <v>533000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>530400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>496000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>555900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>228200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -787,8 +789,11 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -804,14 +809,14 @@
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>37922700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>17920300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>41106700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -822,8 +827,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +845,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +881,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,22 +919,25 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>70100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>56100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>75200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -942,31 +957,34 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -977,8 +995,11 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,31 +1010,32 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>31736000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>17470100</v>
+      </c>
+      <c r="F17" s="3">
+        <v>-16030600</v>
+      </c>
+      <c r="G17" s="3">
+        <v>-73209900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>36849100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>16689800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>39859600</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1024,16 +1046,19 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-309800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>558500</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -1041,14 +1066,14 @@
       <c r="G18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+      <c r="H18" s="3">
+        <v>1569600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1786400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1475300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1059,8 +1084,11 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,16 +1102,17 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1091,14 +1120,14 @@
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1109,8 +1138,11 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,31 +1176,34 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1179,31 +1214,34 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-309800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>558500</v>
+      </c>
+      <c r="F23" s="3">
+        <v>215500</v>
+      </c>
+      <c r="G23" s="3">
+        <v>981800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1569600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1786400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1475300</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1214,31 +1252,34 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>173400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>297100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>318800</v>
+      </c>
+      <c r="I24" s="3">
+        <v>432300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>165800</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1249,8 +1290,11 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,31 +1328,34 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-269000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>385100</v>
+      </c>
+      <c r="F26" s="3">
+        <v>210400</v>
+      </c>
+      <c r="G26" s="3">
+        <v>684700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1250900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1354200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1309500</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1319,31 +1366,34 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-258800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>392700</v>
+      </c>
+      <c r="F27" s="3">
+        <v>211700</v>
+      </c>
+      <c r="G27" s="3">
+        <v>684700</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1256000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1333800</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1354,8 +1404,11 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,31 +1442,34 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>438600</v>
+      </c>
+      <c r="E29" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F29" s="3">
+        <v>53600</v>
+      </c>
+      <c r="G29" s="3">
+        <v>48500</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>345600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1424,8 +1480,11 @@
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1518,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,16 +1556,19 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -1511,14 +1576,14 @@
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1529,31 +1594,34 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>402900</v>
+      </c>
+      <c r="F33" s="3">
+        <v>265200</v>
+      </c>
+      <c r="G33" s="3">
+        <v>733200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1256000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1679300</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1564,8 +1632,11 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,31 +1670,34 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>402900</v>
+      </c>
+      <c r="F35" s="3">
+        <v>265200</v>
+      </c>
+      <c r="G35" s="3">
+        <v>733200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1256000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1679300</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1634,48 +1708,54 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1769,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,28 +1785,29 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>26156100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18536100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>45628200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>31589300</v>
+      </c>
+      <c r="H41" s="3">
+        <v>21022600</v>
+      </c>
+      <c r="I41" s="3">
+        <v>20907800</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1739,31 +1821,34 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1774,28 +1859,31 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>12470500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>15201700</v>
+      </c>
+      <c r="F43" s="3">
+        <v>16842800</v>
+      </c>
+      <c r="G43" s="3">
+        <v>22485100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>10893200</v>
+      </c>
+      <c r="I43" s="3">
+        <v>18273500</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1809,31 +1897,34 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1844,31 +1935,34 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1879,31 +1973,34 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="D46" s="3">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1914,28 +2011,31 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>603002400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>581991300</v>
+      </c>
+      <c r="F47" s="3">
+        <v>571135100</v>
+      </c>
+      <c r="G47" s="3">
+        <v>591510000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>686863200</v>
+      </c>
+      <c r="I47" s="3">
+        <v>663929300</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -1949,28 +2049,31 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>11891600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12226900</v>
+      </c>
+      <c r="F48" s="3">
+        <v>12365900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>14392100</v>
+      </c>
+      <c r="H48" s="3">
+        <v>13345200</v>
+      </c>
+      <c r="I48" s="3">
+        <v>11988500</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -1984,28 +2087,31 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>701300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>669400</v>
+      </c>
+      <c r="F49" s="3">
+        <v>652900</v>
+      </c>
+      <c r="G49" s="3">
+        <v>608200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>552100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>567400</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2019,8 +2125,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2163,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,28 +2201,31 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>2185500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1743100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1836100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1636000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1488000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>15300</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2124,8 +2239,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,28 +2277,31 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
+      <c r="D54" s="3">
+        <v>665723300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>637258000</v>
+      </c>
+      <c r="F54" s="3">
+        <v>654470600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>667287900</v>
+      </c>
+      <c r="H54" s="3">
+        <v>740096100</v>
+      </c>
+      <c r="I54" s="3">
+        <v>724598500</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2194,8 +2315,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2333,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,31 +2349,32 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2259,25 +2385,28 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>38300</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="F58" s="3">
+        <v>37000</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>44600</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2294,28 +2423,31 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>89197100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>116368200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>265906800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>122305000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>153362700</v>
+      </c>
+      <c r="I59" s="3">
+        <v>79812300</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2329,31 +2461,34 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>0</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2364,28 +2499,31 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>7498900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>7076800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>6948000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>7061500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>6615200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>7242600</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2399,28 +2537,31 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>154300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>204000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1049400</v>
+      </c>
+      <c r="G62" s="3">
+        <v>197600</v>
+      </c>
+      <c r="H62" s="3">
+        <v>76500</v>
+      </c>
+      <c r="I62" s="3">
+        <v>353200</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2434,8 +2575,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2613,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2651,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,28 +2689,31 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>659569700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>630770300</v>
+      </c>
+      <c r="F66" s="3">
+        <v>647378500</v>
+      </c>
+      <c r="G66" s="3">
+        <v>660106500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>733140400</v>
+      </c>
+      <c r="I66" s="3">
+        <v>711405100</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2574,8 +2727,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2745,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2781,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,31 +2819,34 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>3</v>
+      <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>3</v>
@@ -2694,8 +2857,11 @@
       <c r="M70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,28 +2895,31 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>4095600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4539400</v>
+      </c>
+      <c r="F72" s="3">
+        <v>5433200</v>
+      </c>
+      <c r="G72" s="3">
+        <v>5239400</v>
+      </c>
+      <c r="H72" s="3">
+        <v>5101700</v>
+      </c>
+      <c r="I72" s="3">
+        <v>11122700</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2764,8 +2933,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2971,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3009,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,28 +3047,31 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>6153600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6487700</v>
+      </c>
+      <c r="F76" s="3">
+        <v>7092100</v>
+      </c>
+      <c r="G76" s="3">
+        <v>7181400</v>
+      </c>
+      <c r="H76" s="3">
+        <v>6955700</v>
+      </c>
+      <c r="I76" s="3">
+        <v>13193500</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2904,8 +3085,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,71 +3123,77 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>402900</v>
+      </c>
+      <c r="F81" s="3">
+        <v>265200</v>
+      </c>
+      <c r="G81" s="3">
+        <v>733200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1256000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1679300</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3014,8 +3204,11 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,31 +3222,32 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3064,8 +3258,11 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3296,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3334,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3372,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3410,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,16 +3448,19 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>7630200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-25792700</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -3274,8 +3486,11 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,17 +3504,18 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-171000</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -3318,14 +3534,17 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3578,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,16 +3616,19 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-274100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-263900</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3429,8 +3654,11 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,16 +3672,17 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-434800</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-1059600</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3479,8 +3708,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3746,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3784,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,16 +3822,19 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>275400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-984400</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3619,16 +3860,19 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-51000</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3654,16 +3898,19 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>7620000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-27092000</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>
@@ -3687,6 +3934,9 @@
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -662,8 +662,7 @@
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
@@ -722,10 +721,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>31426100</v>
+        <v>31537300</v>
       </c>
       <c r="E8" s="3">
-        <v>18028600</v>
+        <v>18092400</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
@@ -734,13 +733,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>38418800</v>
+        <v>38554600</v>
       </c>
       <c r="I8" s="3">
-        <v>18476200</v>
+        <v>18541500</v>
       </c>
       <c r="J8" s="3">
-        <v>41334900</v>
+        <v>41481100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -766,19 +765,19 @@
         <v>3</v>
       </c>
       <c r="F9" s="3">
-        <v>533000</v>
+        <v>534900</v>
       </c>
       <c r="G9" s="3">
-        <v>530400</v>
+        <v>532300</v>
       </c>
       <c r="H9" s="3">
-        <v>496000</v>
+        <v>497800</v>
       </c>
       <c r="I9" s="3">
-        <v>555900</v>
+        <v>557900</v>
       </c>
       <c r="J9" s="3">
-        <v>228200</v>
+        <v>229100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -810,13 +809,13 @@
         <v>3</v>
       </c>
       <c r="H10" s="3">
-        <v>37922700</v>
+        <v>38056900</v>
       </c>
       <c r="I10" s="3">
-        <v>17920300</v>
+        <v>17983600</v>
       </c>
       <c r="J10" s="3">
-        <v>41106700</v>
+        <v>41252100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -928,16 +927,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>119900</v>
+        <v>120300</v>
       </c>
       <c r="E14" s="3">
-        <v>70100</v>
+        <v>70400</v>
       </c>
       <c r="F14" s="3">
-        <v>56100</v>
+        <v>56300</v>
       </c>
       <c r="G14" s="3">
-        <v>75200</v>
+        <v>75500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1017,25 +1016,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>31736000</v>
+        <v>31848200</v>
       </c>
       <c r="E17" s="3">
-        <v>17470100</v>
+        <v>17531900</v>
       </c>
       <c r="F17" s="3">
-        <v>-16030600</v>
+        <v>-16087300</v>
       </c>
       <c r="G17" s="3">
-        <v>-73209900</v>
+        <v>-73468800</v>
       </c>
       <c r="H17" s="3">
-        <v>36849100</v>
+        <v>36979400</v>
       </c>
       <c r="I17" s="3">
-        <v>16689800</v>
+        <v>16748800</v>
       </c>
       <c r="J17" s="3">
-        <v>39859600</v>
+        <v>40000600</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1055,10 +1054,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-309800</v>
+        <v>-310900</v>
       </c>
       <c r="E18" s="3">
-        <v>558500</v>
+        <v>560500</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -1067,13 +1066,13 @@
         <v>3</v>
       </c>
       <c r="H18" s="3">
-        <v>1569600</v>
+        <v>1575200</v>
       </c>
       <c r="I18" s="3">
-        <v>1786400</v>
+        <v>1792700</v>
       </c>
       <c r="J18" s="3">
-        <v>1475300</v>
+        <v>1480500</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1223,25 +1222,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-309800</v>
+        <v>-310900</v>
       </c>
       <c r="E23" s="3">
-        <v>558500</v>
+        <v>560500</v>
       </c>
       <c r="F23" s="3">
-        <v>215500</v>
+        <v>216300</v>
       </c>
       <c r="G23" s="3">
-        <v>981800</v>
+        <v>985300</v>
       </c>
       <c r="H23" s="3">
-        <v>1569600</v>
+        <v>1575200</v>
       </c>
       <c r="I23" s="3">
-        <v>1786400</v>
+        <v>1792700</v>
       </c>
       <c r="J23" s="3">
-        <v>1475300</v>
+        <v>1480500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1261,25 +1260,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-40800</v>
+        <v>-40900</v>
       </c>
       <c r="E24" s="3">
-        <v>173400</v>
+        <v>174000</v>
       </c>
       <c r="F24" s="3">
-        <v>5100</v>
+        <v>-21800</v>
       </c>
       <c r="G24" s="3">
-        <v>297100</v>
+        <v>298100</v>
       </c>
       <c r="H24" s="3">
-        <v>318800</v>
+        <v>319900</v>
       </c>
       <c r="I24" s="3">
-        <v>432300</v>
+        <v>433800</v>
       </c>
       <c r="J24" s="3">
-        <v>165800</v>
+        <v>166300</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1337,25 +1336,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-269000</v>
+        <v>-270000</v>
       </c>
       <c r="E26" s="3">
-        <v>385100</v>
+        <v>386400</v>
       </c>
       <c r="F26" s="3">
-        <v>210400</v>
+        <v>238000</v>
       </c>
       <c r="G26" s="3">
-        <v>684700</v>
+        <v>687200</v>
       </c>
       <c r="H26" s="3">
-        <v>1250900</v>
+        <v>1255300</v>
       </c>
       <c r="I26" s="3">
-        <v>1354200</v>
+        <v>1358900</v>
       </c>
       <c r="J26" s="3">
-        <v>1309500</v>
+        <v>1314200</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1375,25 +1374,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-258800</v>
+        <v>-259800</v>
       </c>
       <c r="E27" s="3">
-        <v>392700</v>
+        <v>394100</v>
       </c>
       <c r="F27" s="3">
-        <v>211700</v>
+        <v>239300</v>
       </c>
       <c r="G27" s="3">
-        <v>684700</v>
+        <v>687200</v>
       </c>
       <c r="H27" s="3">
-        <v>1256000</v>
+        <v>1260400</v>
       </c>
       <c r="I27" s="3">
-        <v>1358000</v>
+        <v>1362800</v>
       </c>
       <c r="J27" s="3">
-        <v>1333800</v>
+        <v>1338500</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1451,16 +1450,16 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>438600</v>
+        <v>440200</v>
       </c>
       <c r="E29" s="3">
         <v>10200</v>
       </c>
       <c r="F29" s="3">
-        <v>53600</v>
+        <v>26900</v>
       </c>
       <c r="G29" s="3">
-        <v>48500</v>
+        <v>48600</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -1469,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>345600</v>
+        <v>346800</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1603,25 +1602,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>179800</v>
+        <v>180400</v>
       </c>
       <c r="E33" s="3">
-        <v>402900</v>
+        <v>404400</v>
       </c>
       <c r="F33" s="3">
-        <v>265200</v>
+        <v>266200</v>
       </c>
       <c r="G33" s="3">
-        <v>733200</v>
+        <v>735800</v>
       </c>
       <c r="H33" s="3">
-        <v>1256000</v>
+        <v>1260400</v>
       </c>
       <c r="I33" s="3">
-        <v>1358000</v>
+        <v>1362800</v>
       </c>
       <c r="J33" s="3">
-        <v>1679300</v>
+        <v>1685200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1679,25 +1678,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>179800</v>
+        <v>180400</v>
       </c>
       <c r="E35" s="3">
-        <v>402900</v>
+        <v>404400</v>
       </c>
       <c r="F35" s="3">
-        <v>265200</v>
+        <v>266200</v>
       </c>
       <c r="G35" s="3">
-        <v>733200</v>
+        <v>735800</v>
       </c>
       <c r="H35" s="3">
-        <v>1256000</v>
+        <v>1260400</v>
       </c>
       <c r="I35" s="3">
-        <v>1358000</v>
+        <v>1362800</v>
       </c>
       <c r="J35" s="3">
-        <v>1679300</v>
+        <v>1685200</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1792,25 +1791,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>26156100</v>
+        <v>26248600</v>
       </c>
       <c r="E41" s="3">
-        <v>18536100</v>
+        <v>18601700</v>
       </c>
       <c r="F41" s="3">
-        <v>45628200</v>
+        <v>45789600</v>
       </c>
       <c r="G41" s="3">
-        <v>31589300</v>
+        <v>31701100</v>
       </c>
       <c r="H41" s="3">
-        <v>21022600</v>
+        <v>21096900</v>
       </c>
       <c r="I41" s="3">
-        <v>20907800</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>20981800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>23058600</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1868,25 +1867,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12470500</v>
+        <v>12514600</v>
       </c>
       <c r="E43" s="3">
-        <v>15201700</v>
+        <v>15255500</v>
       </c>
       <c r="F43" s="3">
-        <v>16842800</v>
+        <v>16902400</v>
       </c>
       <c r="G43" s="3">
-        <v>22485100</v>
+        <v>22564600</v>
       </c>
       <c r="H43" s="3">
-        <v>10893200</v>
+        <v>10931700</v>
       </c>
       <c r="I43" s="3">
-        <v>18273500</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>18338100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>12065400</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2020,25 +2019,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>603002400</v>
+        <v>605135200</v>
       </c>
       <c r="E47" s="3">
-        <v>581991300</v>
+        <v>584049800</v>
       </c>
       <c r="F47" s="3">
-        <v>571135100</v>
+        <v>573155200</v>
       </c>
       <c r="G47" s="3">
-        <v>591510000</v>
+        <v>593602100</v>
       </c>
       <c r="H47" s="3">
-        <v>686863200</v>
+        <v>689292600</v>
       </c>
       <c r="I47" s="3">
-        <v>663929300</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>666277600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>674327600</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2058,25 +2057,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11891600</v>
+        <v>11933600</v>
       </c>
       <c r="E48" s="3">
-        <v>12226900</v>
+        <v>12270200</v>
       </c>
       <c r="F48" s="3">
-        <v>12365900</v>
+        <v>12409700</v>
       </c>
       <c r="G48" s="3">
-        <v>14392100</v>
+        <v>14443000</v>
       </c>
       <c r="H48" s="3">
-        <v>13345200</v>
+        <v>13392400</v>
       </c>
       <c r="I48" s="3">
-        <v>11988500</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>12030900</v>
+      </c>
+      <c r="J48" s="3">
+        <v>11195300</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2096,25 +2095,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>701300</v>
+        <v>703800</v>
       </c>
       <c r="E49" s="3">
-        <v>669400</v>
+        <v>671800</v>
       </c>
       <c r="F49" s="3">
-        <v>652900</v>
+        <v>655200</v>
       </c>
       <c r="G49" s="3">
-        <v>608200</v>
+        <v>610400</v>
       </c>
       <c r="H49" s="3">
-        <v>552100</v>
+        <v>554100</v>
       </c>
       <c r="I49" s="3">
-        <v>567400</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>569400</v>
+      </c>
+      <c r="J49" s="3">
+        <v>508000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2210,25 +2209,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2185500</v>
+        <v>2193300</v>
       </c>
       <c r="E52" s="3">
-        <v>1743100</v>
+        <v>1749200</v>
       </c>
       <c r="F52" s="3">
-        <v>1836100</v>
+        <v>1842600</v>
       </c>
       <c r="G52" s="3">
-        <v>1636000</v>
+        <v>1641700</v>
       </c>
       <c r="H52" s="3">
-        <v>1488000</v>
+        <v>1493300</v>
       </c>
       <c r="I52" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>15400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>6400</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2286,25 +2285,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>665723300</v>
+        <v>668078000</v>
       </c>
       <c r="E54" s="3">
-        <v>637258000</v>
+        <v>639512000</v>
       </c>
       <c r="F54" s="3">
-        <v>654470600</v>
+        <v>656785400</v>
       </c>
       <c r="G54" s="3">
-        <v>667287900</v>
+        <v>669648100</v>
       </c>
       <c r="H54" s="3">
-        <v>740096100</v>
+        <v>742713800</v>
       </c>
       <c r="I54" s="3">
-        <v>724598500</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>727161400</v>
+      </c>
+      <c r="J54" s="3">
+        <v>730100700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2394,25 +2393,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>38300</v>
+        <v>38400</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="3">
-        <v>37000</v>
+        <v>37100</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H58" s="3">
-        <v>44600</v>
+        <v>44800</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>43500</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2432,25 +2431,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>89197100</v>
+        <v>612000400</v>
       </c>
       <c r="E59" s="3">
-        <v>116368200</v>
+        <v>599849200</v>
       </c>
       <c r="F59" s="3">
-        <v>265906800</v>
+        <v>733961300</v>
       </c>
       <c r="G59" s="3">
-        <v>122305000</v>
+        <v>699374700</v>
       </c>
       <c r="H59" s="3">
-        <v>153362700</v>
+        <v>750946800</v>
       </c>
       <c r="I59" s="3">
-        <v>79812300</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>649459700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>622512400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2508,25 +2507,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7498900</v>
+        <v>7525400</v>
       </c>
       <c r="E61" s="3">
-        <v>7076800</v>
+        <v>7101800</v>
       </c>
       <c r="F61" s="3">
-        <v>6948000</v>
+        <v>6972600</v>
       </c>
       <c r="G61" s="3">
-        <v>7061500</v>
+        <v>7086500</v>
       </c>
       <c r="H61" s="3">
-        <v>6615200</v>
+        <v>6638600</v>
       </c>
       <c r="I61" s="3">
-        <v>7242600</v>
+        <v>7268200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>7439700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2546,25 +2545,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>154300</v>
+        <v>154800</v>
       </c>
       <c r="E62" s="3">
-        <v>204000</v>
+        <v>204700</v>
       </c>
       <c r="F62" s="3">
-        <v>1049400</v>
+        <v>1053100</v>
       </c>
       <c r="G62" s="3">
-        <v>197600</v>
+        <v>964800</v>
       </c>
       <c r="H62" s="3">
-        <v>76500</v>
+        <v>76800</v>
       </c>
       <c r="I62" s="3">
-        <v>353200</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>354500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>264900</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2698,25 +2697,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>659569700</v>
+        <v>661902600</v>
       </c>
       <c r="E66" s="3">
-        <v>630770300</v>
+        <v>633001300</v>
       </c>
       <c r="F66" s="3">
-        <v>647378500</v>
+        <v>649668200</v>
       </c>
       <c r="G66" s="3">
-        <v>660106500</v>
+        <v>662441300</v>
       </c>
       <c r="H66" s="3">
-        <v>733140400</v>
+        <v>735733500</v>
       </c>
       <c r="I66" s="3">
-        <v>711405100</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>713921300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>717308400</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2904,25 +2903,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4095600</v>
+        <v>4110100</v>
       </c>
       <c r="E72" s="3">
-        <v>4539400</v>
+        <v>4555400</v>
       </c>
       <c r="F72" s="3">
-        <v>5433200</v>
+        <v>5452400</v>
       </c>
       <c r="G72" s="3">
-        <v>5239400</v>
+        <v>5379500</v>
       </c>
       <c r="H72" s="3">
-        <v>5101700</v>
+        <v>5119700</v>
       </c>
       <c r="I72" s="3">
-        <v>11122700</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>11162000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>10674500</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3056,25 +3055,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6153600</v>
+        <v>6175400</v>
       </c>
       <c r="E76" s="3">
-        <v>6487700</v>
+        <v>6510700</v>
       </c>
       <c r="F76" s="3">
-        <v>7092100</v>
+        <v>7117200</v>
       </c>
       <c r="G76" s="3">
-        <v>7181400</v>
+        <v>7206800</v>
       </c>
       <c r="H76" s="3">
-        <v>6955700</v>
+        <v>6980300</v>
       </c>
       <c r="I76" s="3">
-        <v>13193500</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>13240100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>12792300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3175,25 +3174,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>179800</v>
+        <v>180400</v>
       </c>
       <c r="E81" s="3">
-        <v>402900</v>
+        <v>404400</v>
       </c>
       <c r="F81" s="3">
-        <v>265200</v>
+        <v>266200</v>
       </c>
       <c r="G81" s="3">
-        <v>733200</v>
+        <v>735800</v>
       </c>
       <c r="H81" s="3">
-        <v>1256000</v>
+        <v>1260400</v>
       </c>
       <c r="I81" s="3">
-        <v>1358000</v>
+        <v>1362800</v>
       </c>
       <c r="J81" s="3">
-        <v>1679300</v>
+        <v>1685200</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3457,10 +3456,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>7630200</v>
+        <v>7657200</v>
       </c>
       <c r="E89" s="3">
-        <v>-25792700</v>
+        <v>-25884000</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -3625,10 +3624,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-274100</v>
+        <v>-275100</v>
       </c>
       <c r="E94" s="3">
-        <v>-263900</v>
+        <v>-264900</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3679,10 +3678,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-434800</v>
+        <v>-436300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1059600</v>
+        <v>-1063400</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3831,10 +3830,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>275400</v>
+        <v>276400</v>
       </c>
       <c r="E100" s="3">
-        <v>-984400</v>
+        <v>-987900</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -3872,7 +3871,7 @@
         <v>-11500</v>
       </c>
       <c r="E101" s="3">
-        <v>-51000</v>
+        <v>-51200</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3907,10 +3906,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>7620000</v>
+        <v>7646900</v>
       </c>
       <c r="E102" s="3">
-        <v>-27092000</v>
+        <v>-27187900</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -656,94 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>31537300</v>
+        <v>25980200</v>
       </c>
       <c r="E8" s="3">
-        <v>18092400</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+        <v>32340500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>18643700</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
-        <v>38554600</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I8" s="3">
-        <v>18541500</v>
+        <v>39536600</v>
       </c>
       <c r="J8" s="3">
+        <v>19013800</v>
+      </c>
+      <c r="K8" s="3">
         <v>41481100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,8 +756,11 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -764,24 +770,24 @@
       <c r="E9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="3">
-        <v>534900</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G9" s="3">
-        <v>532300</v>
+        <v>548500</v>
       </c>
       <c r="H9" s="3">
-        <v>497800</v>
+        <v>545900</v>
       </c>
       <c r="I9" s="3">
-        <v>557900</v>
+        <v>510400</v>
       </c>
       <c r="J9" s="3">
+        <v>572100</v>
+      </c>
+      <c r="K9" s="3">
         <v>229100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,8 +797,11 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -808,18 +817,18 @@
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3">
-        <v>38056900</v>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I10" s="3">
-        <v>17983600</v>
+        <v>39026100</v>
       </c>
       <c r="J10" s="3">
+        <v>18441700</v>
+      </c>
+      <c r="K10" s="3">
         <v>41252100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -829,8 +838,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -845,8 +857,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -883,8 +896,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -921,25 +937,28 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>120300</v>
+        <v>114200</v>
       </c>
       <c r="E14" s="3">
-        <v>70400</v>
+        <v>123300</v>
       </c>
       <c r="F14" s="3">
-        <v>56300</v>
+        <v>72200</v>
       </c>
       <c r="G14" s="3">
-        <v>75500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+        <v>57700</v>
+      </c>
+      <c r="H14" s="3">
+        <v>77400</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -959,8 +978,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -985,8 +1007,8 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
@@ -997,8 +1019,11 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1010,35 +1035,36 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>31848200</v>
+        <v>25337300</v>
       </c>
       <c r="E17" s="3">
-        <v>17531900</v>
+        <v>32659300</v>
       </c>
       <c r="F17" s="3">
-        <v>-16087300</v>
+        <v>17978500</v>
       </c>
       <c r="G17" s="3">
-        <v>-73468800</v>
+        <v>-16497000</v>
       </c>
       <c r="H17" s="3">
-        <v>36979400</v>
+        <v>-75340000</v>
       </c>
       <c r="I17" s="3">
-        <v>16748800</v>
+        <v>37921300</v>
       </c>
       <c r="J17" s="3">
+        <v>17175400</v>
+      </c>
+      <c r="K17" s="3">
         <v>40000600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1048,35 +1074,38 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-310900</v>
+        <v>643000</v>
       </c>
       <c r="E18" s="3">
-        <v>560500</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
+        <v>-318900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>665300</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="3">
-        <v>1575200</v>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I18" s="3">
-        <v>1792700</v>
+        <v>1615300</v>
       </c>
       <c r="J18" s="3">
+        <v>1838400</v>
+      </c>
+      <c r="K18" s="3">
         <v>1480500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,8 +1115,11 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1102,8 +1134,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1113,14 +1146,14 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1128,8 +1161,8 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1140,8 +1173,11 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1178,8 +1214,11 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1204,8 +1243,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1216,35 +1255,38 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-310900</v>
+        <v>643000</v>
       </c>
       <c r="E23" s="3">
-        <v>560500</v>
+        <v>-318900</v>
       </c>
       <c r="F23" s="3">
-        <v>216300</v>
+        <v>665300</v>
       </c>
       <c r="G23" s="3">
-        <v>985300</v>
+        <v>221800</v>
       </c>
       <c r="H23" s="3">
-        <v>1575200</v>
+        <v>1010400</v>
       </c>
       <c r="I23" s="3">
-        <v>1792700</v>
+        <v>1615300</v>
       </c>
       <c r="J23" s="3">
+        <v>1838400</v>
+      </c>
+      <c r="K23" s="3">
         <v>1480500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,35 +1296,38 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-40900</v>
+        <v>346400</v>
       </c>
       <c r="E24" s="3">
-        <v>174000</v>
+        <v>-42000</v>
       </c>
       <c r="F24" s="3">
-        <v>-21800</v>
+        <v>189000</v>
       </c>
       <c r="G24" s="3">
-        <v>298100</v>
+        <v>-22300</v>
       </c>
       <c r="H24" s="3">
-        <v>319900</v>
+        <v>305700</v>
       </c>
       <c r="I24" s="3">
-        <v>433800</v>
+        <v>328100</v>
       </c>
       <c r="J24" s="3">
+        <v>444800</v>
+      </c>
+      <c r="K24" s="3">
         <v>166300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1292,8 +1337,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1330,35 +1378,38 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-270000</v>
+        <v>296600</v>
       </c>
       <c r="E26" s="3">
-        <v>386400</v>
+        <v>-276900</v>
       </c>
       <c r="F26" s="3">
-        <v>238000</v>
+        <v>476300</v>
       </c>
       <c r="G26" s="3">
-        <v>687200</v>
+        <v>244100</v>
       </c>
       <c r="H26" s="3">
-        <v>1255300</v>
+        <v>704700</v>
       </c>
       <c r="I26" s="3">
-        <v>1358900</v>
+        <v>1287300</v>
       </c>
       <c r="J26" s="3">
+        <v>1393600</v>
+      </c>
+      <c r="K26" s="3">
         <v>1314200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1368,35 +1419,38 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-259800</v>
+        <v>300500</v>
       </c>
       <c r="E27" s="3">
-        <v>394100</v>
+        <v>-266400</v>
       </c>
       <c r="F27" s="3">
-        <v>239300</v>
+        <v>484200</v>
       </c>
       <c r="G27" s="3">
-        <v>687200</v>
+        <v>245400</v>
       </c>
       <c r="H27" s="3">
-        <v>1260400</v>
+        <v>704700</v>
       </c>
       <c r="I27" s="3">
-        <v>1362800</v>
+        <v>1292500</v>
       </c>
       <c r="J27" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="K27" s="3">
         <v>1338500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1406,8 +1460,11 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1444,35 +1501,38 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>440200</v>
+        <v>-7900</v>
       </c>
       <c r="E29" s="3">
-        <v>10200</v>
+        <v>451400</v>
       </c>
       <c r="F29" s="3">
-        <v>26900</v>
+        <v>10500</v>
       </c>
       <c r="G29" s="3">
-        <v>48600</v>
+        <v>27600</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>49900</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>346800</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1542,11 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1520,8 +1583,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1558,8 +1624,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1569,14 +1638,14 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -1584,8 +1653,8 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1596,35 +1665,38 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>180400</v>
+        <v>292600</v>
       </c>
       <c r="E33" s="3">
-        <v>404400</v>
+        <v>185000</v>
       </c>
       <c r="F33" s="3">
-        <v>266200</v>
+        <v>494700</v>
       </c>
       <c r="G33" s="3">
-        <v>735800</v>
+        <v>272900</v>
       </c>
       <c r="H33" s="3">
-        <v>1260400</v>
+        <v>754500</v>
       </c>
       <c r="I33" s="3">
-        <v>1362800</v>
+        <v>1292500</v>
       </c>
       <c r="J33" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="K33" s="3">
         <v>1685200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1634,8 +1706,11 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1672,35 +1747,38 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>180400</v>
+        <v>292600</v>
       </c>
       <c r="E35" s="3">
-        <v>404400</v>
+        <v>185000</v>
       </c>
       <c r="F35" s="3">
-        <v>266200</v>
+        <v>494700</v>
       </c>
       <c r="G35" s="3">
-        <v>735800</v>
+        <v>272900</v>
       </c>
       <c r="H35" s="3">
-        <v>1260400</v>
+        <v>754500</v>
       </c>
       <c r="I35" s="3">
-        <v>1362800</v>
+        <v>1292500</v>
       </c>
       <c r="J35" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="K35" s="3">
         <v>1685200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1710,51 +1788,57 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1769,8 +1853,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1785,35 +1870,36 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>26248600</v>
+        <v>20740600</v>
       </c>
       <c r="E41" s="3">
-        <v>18601700</v>
+        <v>26917200</v>
       </c>
       <c r="F41" s="3">
-        <v>45789600</v>
+        <v>19075500</v>
       </c>
       <c r="G41" s="3">
-        <v>31701100</v>
+        <v>46955800</v>
       </c>
       <c r="H41" s="3">
-        <v>21096900</v>
+        <v>32508400</v>
       </c>
       <c r="I41" s="3">
-        <v>20981800</v>
+        <v>21634200</v>
       </c>
       <c r="J41" s="3">
+        <v>21516100</v>
+      </c>
+      <c r="K41" s="3">
         <v>23058600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1823,8 +1909,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1849,8 +1938,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -1861,35 +1950,38 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12514600</v>
+        <v>16843400</v>
       </c>
       <c r="E43" s="3">
-        <v>15255500</v>
+        <v>12833300</v>
       </c>
       <c r="F43" s="3">
-        <v>16902400</v>
+        <v>15651900</v>
       </c>
       <c r="G43" s="3">
-        <v>22564600</v>
+        <v>17332800</v>
       </c>
       <c r="H43" s="3">
-        <v>10931700</v>
+        <v>23139300</v>
       </c>
       <c r="I43" s="3">
-        <v>18338100</v>
+        <v>11210100</v>
       </c>
       <c r="J43" s="3">
+        <v>18805100</v>
+      </c>
+      <c r="K43" s="3">
         <v>12065400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,8 +1991,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1925,8 +2020,8 @@
       <c r="J44" s="3">
         <v>0</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -1937,8 +2032,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1963,8 +2061,8 @@
       <c r="J45" s="3">
         <v>0</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -1975,8 +2073,11 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2001,8 +2102,8 @@
       <c r="J46" s="3">
         <v>0</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
+      <c r="K46" s="3">
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
@@ -2013,35 +2114,38 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>605135200</v>
+        <v>626894400</v>
       </c>
       <c r="E47" s="3">
-        <v>584049800</v>
+        <v>620547300</v>
       </c>
       <c r="F47" s="3">
-        <v>573155200</v>
+        <v>598907800</v>
       </c>
       <c r="G47" s="3">
-        <v>593602100</v>
+        <v>587752800</v>
       </c>
       <c r="H47" s="3">
-        <v>689292600</v>
+        <v>608720400</v>
       </c>
       <c r="I47" s="3">
-        <v>666277600</v>
+        <v>706848000</v>
       </c>
       <c r="J47" s="3">
+        <v>683246800</v>
+      </c>
+      <c r="K47" s="3">
         <v>674327600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2051,35 +2155,38 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11933600</v>
+        <v>12716500</v>
       </c>
       <c r="E48" s="3">
-        <v>12270200</v>
+        <v>12237600</v>
       </c>
       <c r="F48" s="3">
-        <v>12409700</v>
+        <v>12582700</v>
       </c>
       <c r="G48" s="3">
-        <v>14443000</v>
+        <v>12725700</v>
       </c>
       <c r="H48" s="3">
-        <v>13392400</v>
+        <v>14810800</v>
       </c>
       <c r="I48" s="3">
-        <v>12030900</v>
+        <v>13733500</v>
       </c>
       <c r="J48" s="3">
+        <v>12337300</v>
+      </c>
+      <c r="K48" s="3">
         <v>11195300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2089,35 +2196,38 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>703800</v>
+        <v>707300</v>
       </c>
       <c r="E49" s="3">
+        <v>721700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>688900</v>
+      </c>
+      <c r="G49" s="3">
         <v>671800</v>
       </c>
-      <c r="F49" s="3">
-        <v>655200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>610400</v>
-      </c>
       <c r="H49" s="3">
-        <v>554100</v>
+        <v>625900</v>
       </c>
       <c r="I49" s="3">
-        <v>569400</v>
+        <v>568200</v>
       </c>
       <c r="J49" s="3">
+        <v>583900</v>
+      </c>
+      <c r="K49" s="3">
         <v>508000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,8 +2237,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2165,8 +2278,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2203,35 +2319,38 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2193300</v>
+        <v>2257000</v>
       </c>
       <c r="E52" s="3">
-        <v>1749200</v>
+        <v>2249100</v>
       </c>
       <c r="F52" s="3">
-        <v>1842600</v>
+        <v>1759700</v>
       </c>
       <c r="G52" s="3">
-        <v>1641700</v>
+        <v>1889600</v>
       </c>
       <c r="H52" s="3">
-        <v>1493300</v>
+        <v>1683600</v>
       </c>
       <c r="I52" s="3">
-        <v>15400</v>
+        <v>1531300</v>
       </c>
       <c r="J52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K52" s="3">
         <v>6400</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2241,8 +2360,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2279,35 +2401,38 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>668078000</v>
+        <v>690898200</v>
       </c>
       <c r="E54" s="3">
-        <v>639512000</v>
+        <v>685093100</v>
       </c>
       <c r="F54" s="3">
-        <v>656785400</v>
+        <v>655786400</v>
       </c>
       <c r="G54" s="3">
-        <v>669648100</v>
+        <v>673512900</v>
       </c>
       <c r="H54" s="3">
-        <v>742713800</v>
+        <v>686703100</v>
       </c>
       <c r="I54" s="3">
-        <v>727161400</v>
+        <v>761629700</v>
       </c>
       <c r="J54" s="3">
+        <v>745681300</v>
+      </c>
+      <c r="K54" s="3">
         <v>730100700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2317,8 +2442,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2333,8 +2461,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2349,8 +2478,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2375,8 +2505,8 @@
       <c r="J57" s="3">
         <v>0</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
+      <c r="K57" s="3">
+        <v>0</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
@@ -2387,35 +2517,38 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>38400</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3">
-        <v>37100</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3">
-        <v>44800</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
+        <v>38100</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
+        <v>45900</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
         <v>43500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2425,35 +2558,38 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>612000400</v>
+        <v>570946100</v>
       </c>
       <c r="E59" s="3">
-        <v>599849200</v>
+        <v>627587200</v>
       </c>
       <c r="F59" s="3">
-        <v>733961300</v>
+        <v>652381200</v>
       </c>
       <c r="G59" s="3">
-        <v>699374700</v>
+        <v>752654300</v>
       </c>
       <c r="H59" s="3">
-        <v>750946800</v>
+        <v>717186800</v>
       </c>
       <c r="I59" s="3">
-        <v>649459700</v>
+        <v>770072400</v>
       </c>
       <c r="J59" s="3">
+        <v>666000500</v>
+      </c>
+      <c r="K59" s="3">
         <v>622512400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2463,8 +2599,11 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2489,8 +2628,8 @@
       <c r="J60" s="3">
         <v>0</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
+      <c r="K60" s="3">
+        <v>0</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
@@ -2501,35 +2640,38 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7525400</v>
+        <v>7965100</v>
       </c>
       <c r="E61" s="3">
-        <v>7101800</v>
+        <v>7717000</v>
       </c>
       <c r="F61" s="3">
-        <v>6972600</v>
+        <v>7189500</v>
       </c>
       <c r="G61" s="3">
-        <v>7086500</v>
+        <v>7150200</v>
       </c>
       <c r="H61" s="3">
-        <v>6638600</v>
+        <v>7267000</v>
       </c>
       <c r="I61" s="3">
-        <v>7268200</v>
+        <v>6807700</v>
       </c>
       <c r="J61" s="3">
+        <v>7453300</v>
+      </c>
+      <c r="K61" s="3">
         <v>7439700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2539,35 +2681,38 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>154800</v>
+        <v>249300</v>
       </c>
       <c r="E62" s="3">
-        <v>204700</v>
+        <v>158800</v>
       </c>
       <c r="F62" s="3">
-        <v>1053100</v>
+        <v>2068000</v>
       </c>
       <c r="G62" s="3">
-        <v>964800</v>
+        <v>1079900</v>
       </c>
       <c r="H62" s="3">
-        <v>76800</v>
+        <v>989400</v>
       </c>
       <c r="I62" s="3">
-        <v>354500</v>
+        <v>78700</v>
       </c>
       <c r="J62" s="3">
+        <v>363500</v>
+      </c>
+      <c r="K62" s="3">
         <v>264900</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,8 +2722,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2615,8 +2763,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2653,8 +2804,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2691,35 +2845,38 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>661902600</v>
+        <v>685704500</v>
       </c>
       <c r="E66" s="3">
-        <v>633001300</v>
+        <v>678760400</v>
       </c>
       <c r="F66" s="3">
-        <v>649668200</v>
+        <v>649087600</v>
       </c>
       <c r="G66" s="3">
-        <v>662441300</v>
+        <v>666214400</v>
       </c>
       <c r="H66" s="3">
-        <v>735733500</v>
+        <v>679312800</v>
       </c>
       <c r="I66" s="3">
-        <v>713921300</v>
+        <v>754471700</v>
       </c>
       <c r="J66" s="3">
+        <v>732103900</v>
+      </c>
+      <c r="K66" s="3">
         <v>717308400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,8 +2886,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2745,8 +2905,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2783,8 +2944,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2821,8 +2985,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2847,8 +3014,8 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>3</v>
+      <c r="K70" s="3">
+        <v>0</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>3</v>
@@ -2859,8 +3026,11 @@
       <c r="N70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2897,35 +3067,38 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4110100</v>
+        <v>3178100</v>
       </c>
       <c r="E72" s="3">
-        <v>4555400</v>
+        <v>4214800</v>
       </c>
       <c r="F72" s="3">
-        <v>5452400</v>
+        <v>4693700</v>
       </c>
       <c r="G72" s="3">
-        <v>5379500</v>
+        <v>5591300</v>
       </c>
       <c r="H72" s="3">
-        <v>5119700</v>
+        <v>5516500</v>
       </c>
       <c r="I72" s="3">
-        <v>11162000</v>
+        <v>5250100</v>
       </c>
       <c r="J72" s="3">
+        <v>11446300</v>
+      </c>
+      <c r="K72" s="3">
         <v>10674500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,8 +3108,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2973,8 +3149,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3011,8 +3190,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3049,35 +3231,38 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6175400</v>
+        <v>5193700</v>
       </c>
       <c r="E76" s="3">
-        <v>6510700</v>
+        <v>6332700</v>
       </c>
       <c r="F76" s="3">
-        <v>7117200</v>
+        <v>6698800</v>
       </c>
       <c r="G76" s="3">
-        <v>7206800</v>
+        <v>7298500</v>
       </c>
       <c r="H76" s="3">
-        <v>6980300</v>
+        <v>7390300</v>
       </c>
       <c r="I76" s="3">
-        <v>13240100</v>
+        <v>7158100</v>
       </c>
       <c r="J76" s="3">
+        <v>13577300</v>
+      </c>
+      <c r="K76" s="3">
         <v>12792300</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,8 +3272,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3125,78 +3313,84 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>180400</v>
+        <v>292600</v>
       </c>
       <c r="E81" s="3">
-        <v>404400</v>
+        <v>185000</v>
       </c>
       <c r="F81" s="3">
-        <v>266200</v>
+        <v>494700</v>
       </c>
       <c r="G81" s="3">
-        <v>735800</v>
+        <v>272900</v>
       </c>
       <c r="H81" s="3">
-        <v>1260400</v>
+        <v>754500</v>
       </c>
       <c r="I81" s="3">
-        <v>1362800</v>
+        <v>1292500</v>
       </c>
       <c r="J81" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="K81" s="3">
         <v>1685200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3206,8 +3400,11 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3222,8 +3419,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3248,8 +3446,8 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3260,8 +3458,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3298,8 +3499,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3336,8 +3540,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3374,8 +3581,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3412,8 +3622,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3450,19 +3663,22 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>7657200</v>
+        <v>-4813100</v>
       </c>
       <c r="E89" s="3">
-        <v>-25884000</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
+        <v>7852200</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-26543200</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
@@ -3488,8 +3704,11 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3504,20 +3723,21 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-171000</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -3536,14 +3756,17 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3580,8 +3803,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3618,19 +3844,22 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-275100</v>
+        <v>-124700</v>
       </c>
       <c r="E94" s="3">
-        <v>-264900</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+        <v>-282100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-271600</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -3656,8 +3885,11 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3672,19 +3904,20 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-436300</v>
+        <v>-1146900</v>
       </c>
       <c r="E96" s="3">
-        <v>-1063400</v>
+        <v>-447500</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-1090400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3710,8 +3943,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3748,8 +3984,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3786,8 +4025,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3824,19 +4066,22 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>276400</v>
+        <v>-1242700</v>
       </c>
       <c r="E100" s="3">
-        <v>-987900</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
+        <v>283400</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-1013000</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -3862,19 +4107,22 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-11500</v>
+        <v>3900</v>
       </c>
       <c r="E101" s="3">
-        <v>-51200</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+        <v>-11800</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-52500</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
@@ -3900,19 +4148,22 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>7646900</v>
+        <v>-6176500</v>
       </c>
       <c r="E102" s="3">
-        <v>-27187900</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
+        <v>7841700</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-27880300</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>
@@ -3936,6 +4187,9 @@
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -686,22 +686,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -723,14 +723,14 @@
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>25980200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>32340500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>18643700</v>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -738,11 +738,11 @@
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
-        <v>39536600</v>
-      </c>
-      <c r="J8" s="3">
-        <v>19013800</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>41481100</v>
@@ -773,17 +773,17 @@
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="3">
-        <v>548500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>545900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>510400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>572100</v>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>229100</v>
@@ -820,11 +820,11 @@
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3">
-        <v>39026100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>18441700</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>41252100</v>
@@ -945,20 +945,20 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>114200</v>
-      </c>
-      <c r="E14" s="3">
-        <v>123300</v>
-      </c>
-      <c r="F14" s="3">
-        <v>72200</v>
-      </c>
-      <c r="G14" s="3">
-        <v>57700</v>
-      </c>
-      <c r="H14" s="3">
-        <v>77400</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -986,26 +986,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1041,26 +1041,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>25337300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>32659300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>17978500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>-16497000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>-75340000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>37921300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>17175400</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>40000600</v>
@@ -1082,14 +1082,14 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>643000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-318900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>665300</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>3</v>
@@ -1097,11 +1097,11 @@
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="3">
-        <v>1615300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1838400</v>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>1480500</v>
@@ -1140,14 +1140,14 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
@@ -1155,11 +1155,11 @@
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1222,26 +1222,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1263,26 +1263,26 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>643000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-318900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>665300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>221800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1010400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1615300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1838400</v>
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>1480500</v>
@@ -1304,26 +1304,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>346400</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-42000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>189000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-22300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>305700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>328100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>444800</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>166300</v>
@@ -1386,26 +1386,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>296600</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-276900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>476300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>244100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>704700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1287300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1393600</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>1314200</v>
@@ -1427,26 +1427,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>300500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-266400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>484200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>245400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>704700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1292500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1397500</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>1338500</v>
@@ -1509,26 +1509,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="E29" s="3">
-        <v>451400</v>
-      </c>
-      <c r="F29" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G29" s="3">
-        <v>27600</v>
-      </c>
-      <c r="H29" s="3">
-        <v>49900</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>346800</v>
@@ -1632,14 +1632,14 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
@@ -1647,11 +1647,11 @@
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1673,26 +1673,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>292600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>185000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>494700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>272900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>754500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1292500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1397500</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>1685200</v>
@@ -1755,26 +1755,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>292600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>185000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>494700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>272900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>754500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1292500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1397500</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>1685200</v>
@@ -1805,22 +1805,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -1877,25 +1877,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>20740600</v>
+        <v>19975500</v>
       </c>
       <c r="E41" s="3">
-        <v>26917200</v>
+        <v>19962600</v>
       </c>
       <c r="F41" s="3">
-        <v>19075500</v>
+        <v>26128500</v>
       </c>
       <c r="G41" s="3">
-        <v>46955800</v>
+        <v>25032300</v>
       </c>
       <c r="H41" s="3">
-        <v>32508400</v>
+        <v>18473500</v>
       </c>
       <c r="I41" s="3">
-        <v>21634200</v>
+        <v>17984200</v>
       </c>
       <c r="J41" s="3">
-        <v>21516100</v>
+        <v>43115900</v>
       </c>
       <c r="K41" s="3">
         <v>23058600</v>
@@ -1924,10 +1924,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>587601300</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>562948800</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>527884800</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1959,25 +1959,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16843400</v>
+        <v>17260900</v>
       </c>
       <c r="E43" s="3">
-        <v>12833300</v>
+        <v>17249700</v>
       </c>
       <c r="F43" s="3">
-        <v>15651900</v>
+        <v>8753200</v>
       </c>
       <c r="G43" s="3">
-        <v>17332800</v>
+        <v>8386000</v>
       </c>
       <c r="H43" s="3">
-        <v>23139300</v>
+        <v>16304300</v>
       </c>
       <c r="I43" s="3">
-        <v>11210100</v>
+        <v>15872400</v>
       </c>
       <c r="J43" s="3">
-        <v>18805100</v>
+        <v>12475500</v>
       </c>
       <c r="K43" s="3">
         <v>12065400</v>
@@ -1999,26 +1999,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>2460900</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+        <v>2357700</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>2377300</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2041,25 +2041,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>65233100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>65191100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>10170900</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>9744200</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>66268100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>64512800</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>6479900</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2082,25 +2082,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>102469400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>102403400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>635619300</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>608952200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>101045900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>98369500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>592796000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2123,25 +2123,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>626894400</v>
+        <v>538759200</v>
       </c>
       <c r="E47" s="3">
-        <v>620547300</v>
+        <v>538412200</v>
       </c>
       <c r="F47" s="3">
-        <v>598907800</v>
+        <v>13591000</v>
       </c>
       <c r="G47" s="3">
-        <v>587752800</v>
+        <v>13020800</v>
       </c>
       <c r="H47" s="3">
-        <v>608720400</v>
+        <v>504085600</v>
       </c>
       <c r="I47" s="3">
-        <v>706848000</v>
+        <v>490733900</v>
       </c>
       <c r="J47" s="3">
-        <v>683246800</v>
+        <v>10697000</v>
       </c>
       <c r="K47" s="3">
         <v>674327600</v>
@@ -2164,25 +2164,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12716500</v>
+        <v>539600</v>
       </c>
       <c r="E48" s="3">
-        <v>12237600</v>
+        <v>539300</v>
       </c>
       <c r="F48" s="3">
-        <v>12582700</v>
+        <v>551500</v>
       </c>
       <c r="G48" s="3">
-        <v>12725700</v>
+        <v>528400</v>
       </c>
       <c r="H48" s="3">
-        <v>14810800</v>
+        <v>460000</v>
       </c>
       <c r="I48" s="3">
-        <v>13733500</v>
+        <v>447800</v>
       </c>
       <c r="J48" s="3">
-        <v>12337300</v>
+        <v>392800</v>
       </c>
       <c r="K48" s="3">
         <v>11195300</v>
@@ -2205,25 +2205,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>707300</v>
+        <v>681200</v>
       </c>
       <c r="E49" s="3">
-        <v>721700</v>
+        <v>680700</v>
       </c>
       <c r="F49" s="3">
-        <v>688900</v>
+        <v>700600</v>
       </c>
       <c r="G49" s="3">
-        <v>671800</v>
+        <v>671200</v>
       </c>
       <c r="H49" s="3">
-        <v>625900</v>
+        <v>673500</v>
       </c>
       <c r="I49" s="3">
-        <v>568200</v>
+        <v>655700</v>
       </c>
       <c r="J49" s="3">
-        <v>583900</v>
+        <v>616900</v>
       </c>
       <c r="K49" s="3">
         <v>508000</v>
@@ -2328,25 +2328,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2257000</v>
+        <v>11707800</v>
       </c>
       <c r="E52" s="3">
-        <v>2249100</v>
+        <v>11700200</v>
       </c>
       <c r="F52" s="3">
-        <v>1759700</v>
+        <v>12359300</v>
       </c>
       <c r="G52" s="3">
-        <v>1889600</v>
+        <v>11840700</v>
       </c>
       <c r="H52" s="3">
-        <v>1683600</v>
+        <v>11725600</v>
       </c>
       <c r="I52" s="3">
-        <v>1531300</v>
+        <v>11415000</v>
       </c>
       <c r="J52" s="3">
-        <v>15700</v>
+        <v>12195900</v>
       </c>
       <c r="K52" s="3">
         <v>6400</v>
@@ -2410,25 +2410,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>690898200</v>
+        <v>665410000</v>
       </c>
       <c r="E54" s="3">
-        <v>685093100</v>
+        <v>664981400</v>
       </c>
       <c r="F54" s="3">
-        <v>655786400</v>
+        <v>665021400</v>
       </c>
       <c r="G54" s="3">
-        <v>673512900</v>
+        <v>637120800</v>
       </c>
       <c r="H54" s="3">
-        <v>686703100</v>
+        <v>635105700</v>
       </c>
       <c r="I54" s="3">
-        <v>761629700</v>
+        <v>618283600</v>
       </c>
       <c r="J54" s="3">
-        <v>745681300</v>
+        <v>618434800</v>
       </c>
       <c r="K54" s="3">
         <v>730100700</v>
@@ -2485,25 +2485,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>179500</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>179300</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>280200</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>268500</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>175400</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>170700</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>62700</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2525,26 +2525,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>28049800</v>
       </c>
       <c r="E58" s="3">
-        <v>39400</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+        <v>28031800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>75735000</v>
       </c>
       <c r="G58" s="3">
-        <v>38100</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+        <v>72557500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>36023200</v>
       </c>
       <c r="I58" s="3">
-        <v>45900</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>35069000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>83805000</v>
       </c>
       <c r="K58" s="3">
         <v>43500</v>
@@ -2567,25 +2567,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>570946100</v>
+        <v>63322300</v>
       </c>
       <c r="E59" s="3">
-        <v>627587200</v>
+        <v>63281500</v>
       </c>
       <c r="F59" s="3">
-        <v>652381200</v>
+        <v>58429700</v>
       </c>
       <c r="G59" s="3">
-        <v>752654300</v>
+        <v>55978300</v>
       </c>
       <c r="H59" s="3">
-        <v>717186800</v>
+        <v>69859300</v>
       </c>
       <c r="I59" s="3">
-        <v>770072400</v>
+        <v>68009000</v>
       </c>
       <c r="J59" s="3">
-        <v>666000500</v>
+        <v>60159000</v>
       </c>
       <c r="K59" s="3">
         <v>622512400</v>
@@ -2608,25 +2608,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>91551600</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>91492600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>135092000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>129424300</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>106057900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>103248700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>144649700</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2649,25 +2649,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7965100</v>
+        <v>7695200</v>
       </c>
       <c r="E61" s="3">
-        <v>7717000</v>
+        <v>7690300</v>
       </c>
       <c r="F61" s="3">
-        <v>7189500</v>
+        <v>7901100</v>
       </c>
       <c r="G61" s="3">
-        <v>7150200</v>
+        <v>7569600</v>
       </c>
       <c r="H61" s="3">
-        <v>7267000</v>
+        <v>7052900</v>
       </c>
       <c r="I61" s="3">
-        <v>6807700</v>
+        <v>6866100</v>
       </c>
       <c r="J61" s="3">
-        <v>7453300</v>
+        <v>6810000</v>
       </c>
       <c r="K61" s="3">
         <v>7439700</v>
@@ -2690,25 +2690,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>249300</v>
+        <v>560976700</v>
       </c>
       <c r="E62" s="3">
-        <v>158800</v>
+        <v>560615300</v>
       </c>
       <c r="F62" s="3">
-        <v>2068000</v>
+        <v>515743600</v>
       </c>
       <c r="G62" s="3">
-        <v>1079900</v>
+        <v>494105900</v>
       </c>
       <c r="H62" s="3">
-        <v>989400</v>
+        <v>513570800</v>
       </c>
       <c r="I62" s="3">
-        <v>78700</v>
+        <v>499967800</v>
       </c>
       <c r="J62" s="3">
-        <v>363500</v>
+        <v>459300000</v>
       </c>
       <c r="K62" s="3">
         <v>264900</v>
@@ -2854,25 +2854,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>685704500</v>
+        <v>660463600</v>
       </c>
       <c r="E66" s="3">
-        <v>678760400</v>
+        <v>660038100</v>
       </c>
       <c r="F66" s="3">
-        <v>649087600</v>
+        <v>658927800</v>
       </c>
       <c r="G66" s="3">
-        <v>666214400</v>
+        <v>631282800</v>
       </c>
       <c r="H66" s="3">
-        <v>679312800</v>
+        <v>628684300</v>
       </c>
       <c r="I66" s="3">
-        <v>754471700</v>
+        <v>612032400</v>
       </c>
       <c r="J66" s="3">
-        <v>732103900</v>
+        <v>611768200</v>
       </c>
       <c r="K66" s="3">
         <v>717308400</v>
@@ -3076,25 +3076,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3178100</v>
+        <v>2650200</v>
       </c>
       <c r="E72" s="3">
-        <v>4214800</v>
+        <v>2648500</v>
       </c>
       <c r="F72" s="3">
-        <v>4693700</v>
+        <v>3786900</v>
       </c>
       <c r="G72" s="3">
-        <v>5591300</v>
+        <v>3628000</v>
       </c>
       <c r="H72" s="3">
-        <v>5516500</v>
+        <v>4084300</v>
       </c>
       <c r="I72" s="3">
-        <v>5250100</v>
+        <v>3976100</v>
       </c>
       <c r="J72" s="3">
-        <v>11446300</v>
+        <v>4466500</v>
       </c>
       <c r="K72" s="3">
         <v>10674500</v>
@@ -3240,25 +3240,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5193700</v>
+        <v>5002100</v>
       </c>
       <c r="E76" s="3">
-        <v>6332700</v>
+        <v>4998900</v>
       </c>
       <c r="F76" s="3">
-        <v>6698800</v>
+        <v>6147100</v>
       </c>
       <c r="G76" s="3">
-        <v>7298500</v>
+        <v>5889200</v>
       </c>
       <c r="H76" s="3">
-        <v>7390300</v>
+        <v>6465800</v>
       </c>
       <c r="I76" s="3">
-        <v>7158100</v>
+        <v>6294500</v>
       </c>
       <c r="J76" s="3">
-        <v>13577300</v>
+        <v>6701600</v>
       </c>
       <c r="K76" s="3">
         <v>12792300</v>
@@ -3330,22 +3330,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -3367,26 +3367,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>292600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>185000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>494700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>272900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>754500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1292500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1397500</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>1685200</v>
@@ -3425,26 +3425,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>33700</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>31200</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3672,25 +3672,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4813100</v>
+        <v>-2317800</v>
       </c>
       <c r="E89" s="3">
-        <v>7852200</v>
+        <v>-2316300</v>
       </c>
       <c r="F89" s="3">
-        <v>-26543200</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>3811100</v>
+      </c>
+      <c r="G89" s="3">
+        <v>3651200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-12852800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-12512400</v>
+      </c>
+      <c r="J89" s="3">
+        <v>6926300</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3730,25 +3730,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-29000</v>
+        <v>-18300</v>
       </c>
       <c r="E91" s="3">
-        <v>-66000</v>
+        <v>-18300</v>
       </c>
       <c r="F91" s="3">
-        <v>-171000</v>
+        <v>-42000</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-40300</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-108700</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-105800</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-76500</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3853,25 +3853,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-124700</v>
+        <v>-60000</v>
       </c>
       <c r="E94" s="3">
-        <v>-282100</v>
+        <v>-60000</v>
       </c>
       <c r="F94" s="3">
-        <v>-271600</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-136900</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-131200</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-131500</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-102400</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3911,25 +3911,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1146900</v>
+        <v>561100</v>
       </c>
       <c r="E96" s="3">
-        <v>-447500</v>
+        <v>560800</v>
       </c>
       <c r="F96" s="3">
-        <v>-1090400</v>
+        <v>226100</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>216600</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>536900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>522700</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>203600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4075,25 +4075,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1242700</v>
+        <v>-598400</v>
       </c>
       <c r="E100" s="3">
-        <v>283400</v>
+        <v>-598000</v>
       </c>
       <c r="F100" s="3">
-        <v>-1013000</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>137600</v>
+      </c>
+      <c r="G100" s="3">
+        <v>131800</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-490500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-477500</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-204200</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -4116,25 +4116,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3900</v>
+        <v>-25400</v>
       </c>
       <c r="E101" s="3">
-        <v>-11800</v>
+        <v>-24700</v>
       </c>
       <c r="F101" s="3">
-        <v>-52500</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>13300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>42500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>46000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>10800</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4157,25 +4157,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6176500</v>
+        <v>-2974300</v>
       </c>
       <c r="E102" s="3">
-        <v>7841700</v>
+        <v>-2972400</v>
       </c>
       <c r="F102" s="3">
-        <v>-27880300</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>3806000</v>
+      </c>
+      <c r="G102" s="3">
+        <v>3646300</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-13500300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-13142700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>6632900</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -656,70 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -744,23 +750,29 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>41481100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,23 +797,29 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>229100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -826,23 +844,29 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>41252100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -858,8 +882,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -899,8 +925,14 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -940,8 +972,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -981,8 +1019,14 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1007,14 +1051,14 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1022,8 +1066,14 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1036,8 +1086,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1062,23 +1114,29 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
         <v>40000600</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1103,23 +1161,29 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>1480500</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1135,8 +1199,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1161,14 +1227,14 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1176,8 +1242,14 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1217,8 +1289,14 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1243,14 +1321,14 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1258,8 +1336,14 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1284,23 +1368,29 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
         <v>1480500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1325,23 +1415,29 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>166300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1381,8 +1477,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1407,23 +1509,29 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
         <v>1314200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1448,23 +1556,29 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
         <v>1338500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1504,8 +1618,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1530,23 +1650,29 @@
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3">
         <v>346800</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1586,8 +1712,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1627,8 +1759,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1653,14 +1791,14 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1668,8 +1806,14 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1694,23 +1838,29 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3">
         <v>1685200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1750,8 +1900,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1776,69 +1932,81 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
         <v>1685200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1854,8 +2022,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1871,81 +2041,89 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20853300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>22325400</v>
+      </c>
+      <c r="F41" s="3">
         <v>19975500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>19962600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>26128500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>25032300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>18473500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17984200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>43115900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>23058600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>606605200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>649427700</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>587601300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>562948800</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>527884800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -1953,81 +2131,93 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9125300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9769500</v>
+      </c>
+      <c r="F43" s="3">
         <v>17260900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>17249700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8753200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8386000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>16304300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>15872400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>12475500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>12065400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="D44" s="3">
+        <v>664800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>711700</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>2460900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2357700</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>2377300</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
@@ -2035,40 +2225,46 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12114900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>12970100</v>
+      </c>
+      <c r="F45" s="3">
         <v>65233100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>65191100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>10170900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>9744200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>66268100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>64512800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>6479900</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2076,40 +2272,46 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>649832900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>695707000</v>
+      </c>
+      <c r="F46" s="3">
         <v>102469400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>102403400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>635619300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>608952200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>101045900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>98369500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>592796000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
+      <c r="M46" s="3">
+        <v>0</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
@@ -2117,131 +2319,155 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14721400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>15760600</v>
+      </c>
+      <c r="F47" s="3">
         <v>538759200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>538412200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>13591000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>13020800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>504085600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>490733900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10697000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>674327600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>494500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>529400</v>
+      </c>
+      <c r="F48" s="3">
         <v>539600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>539300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>551500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>528400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>460000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>447800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>392800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>11195300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>600900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>643300</v>
+      </c>
+      <c r="F49" s="3">
         <v>681200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>680700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>700600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>671200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>673500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>655700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>616900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>508000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2281,8 +2507,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2322,49 +2554,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13321700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>14262200</v>
+      </c>
+      <c r="F52" s="3">
         <v>11707800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>11700200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>12359300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>11840700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>11725600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>11415000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12195900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>6400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2404,49 +2648,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>681256200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>729348600</v>
+      </c>
+      <c r="F54" s="3">
         <v>665410000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>664981400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>665021400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>637120800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>635105700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>618283600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>618434800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>730100700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2462,8 +2718,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2479,40 +2737,42 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>212800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>227900</v>
+      </c>
+      <c r="F57" s="3">
         <v>179500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>179300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>280200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>268500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>175400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>170700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>62700</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2520,122 +2780,140 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>68540400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>73378900</v>
+      </c>
+      <c r="F58" s="3">
         <v>28049800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>28031800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>75735000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>72557500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>36023200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>35069000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>83805000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>43500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>72083300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>77172000</v>
+      </c>
+      <c r="F59" s="3">
         <v>63322300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>63281500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>58429700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>55978300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>69859300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>68009000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>60159000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>622512400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141583900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>151578900</v>
+      </c>
+      <c r="F60" s="3">
         <v>91551600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>91492600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>135092000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>129424300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>106057900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>103248700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>144649700</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
+      <c r="M60" s="3">
+        <v>0</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
@@ -2643,90 +2921,108 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9712400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10398100</v>
+      </c>
+      <c r="F61" s="3">
         <v>7695200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7690300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7901100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7569600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7052900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6866100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6810000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7439700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>525298900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>562381700</v>
+      </c>
+      <c r="F62" s="3">
         <v>560976700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>560615300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>515743600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>494105900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>513570800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>499967800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>459300000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>264900</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2766,8 +3062,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2807,8 +3109,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2848,49 +3156,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>676860700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>724642800</v>
+      </c>
+      <c r="F66" s="3">
         <v>660463600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>660038100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>658927800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>631282800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>628684300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>612032400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>611768200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>717308400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2906,8 +3226,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2947,8 +3269,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2988,8 +3316,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3017,11 +3351,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>3</v>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>3</v>
@@ -3029,8 +3363,14 @@
       <c r="O70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3070,49 +3410,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2145800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2297300</v>
+      </c>
+      <c r="F72" s="3">
         <v>2650200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2648500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3786900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3628000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4084300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3976100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4466500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>10674500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3152,8 +3504,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3193,8 +3551,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3234,49 +3598,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4441800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4755400</v>
+      </c>
+      <c r="F76" s="3">
         <v>5002100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4998900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6147100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5889200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6465800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6294500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6701600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12792300</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3316,54 +3692,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3388,23 +3776,29 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3">
         <v>1685200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3420,40 +3814,42 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>29300</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>33700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>31200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>35900</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3461,8 +3857,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3502,8 +3904,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3543,8 +3951,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3584,8 +3998,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3625,8 +4045,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3666,38 +4092,44 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-487000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-521400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2317800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2316300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>3811100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>3651200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-12852800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-12512400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>6926300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3707,8 +4139,14 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3724,49 +4162,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-44200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-18300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-18300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-42000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-40300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-108700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-105800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-76500</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3806,8 +4252,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3847,38 +4299,44 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>209100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>223800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-60000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-60000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-136900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-131200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-131500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-128000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-102400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3888,8 +4346,14 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3905,38 +4369,40 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>231600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>248000</v>
+      </c>
+      <c r="F96" s="3">
         <v>561100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>560800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>226100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>216600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>536900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>522700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>203600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -3946,8 +4412,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3987,8 +4459,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4028,8 +4506,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4069,38 +4553,44 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>856500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-598400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-598000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>137600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>131800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-490500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-477500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-204200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4110,38 +4600,44 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-25400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-24700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>13300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>12300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>42500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>46000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>10800</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,38 +4647,44 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>532700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>570300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2974300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2972400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3806000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3646300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-13500300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-13142700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6632900</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4190,6 +4692,12 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -2792,10 +2792,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>68540400</v>
+        <v>80349800</v>
       </c>
       <c r="E58" s="3">
-        <v>73378900</v>
+        <v>86022000</v>
       </c>
       <c r="F58" s="3">
         <v>28049800</v>
@@ -2839,10 +2839,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>72083300</v>
+        <v>67299700</v>
       </c>
       <c r="E59" s="3">
-        <v>77172000</v>
+        <v>72050700</v>
       </c>
       <c r="F59" s="3">
         <v>63322300</v>
@@ -2886,10 +2886,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>141583900</v>
+        <v>148609700</v>
       </c>
       <c r="E60" s="3">
-        <v>151578900</v>
+        <v>159100700</v>
       </c>
       <c r="F60" s="3">
         <v>91551600</v>
@@ -2980,10 +2980,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>525298900</v>
+        <v>518273100</v>
       </c>
       <c r="E62" s="3">
-        <v>562381700</v>
+        <v>554859900</v>
       </c>
       <c r="F62" s="3">
         <v>560976700</v>

--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -656,76 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -756,23 +762,29 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3">
         <v>41481100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -803,23 +815,29 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3">
         <v>229100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,23 +868,29 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3">
         <v>41252100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -884,8 +908,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -931,8 +957,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -978,8 +1010,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1025,8 +1063,14 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1057,14 +1101,14 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1072,8 +1116,14 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1088,8 +1138,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1120,23 +1172,29 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3">
         <v>40000600</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1167,23 +1225,29 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>1480500</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1201,8 +1265,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1233,14 +1299,14 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1248,8 +1314,14 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1295,8 +1367,14 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1327,14 +1405,14 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1342,8 +1420,14 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1374,23 +1458,29 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3">
         <v>1480500</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1421,23 +1511,29 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3">
         <v>166300</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1483,8 +1579,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1515,23 +1617,29 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3">
         <v>1314200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1562,23 +1670,29 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3">
         <v>1338500</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1624,8 +1738,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1656,23 +1776,29 @@
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3">
         <v>346800</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1718,8 +1844,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1765,8 +1897,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1797,14 +1935,14 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1812,8 +1950,14 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1844,23 +1988,29 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3">
         <v>1685200</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1906,8 +2056,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1938,75 +2094,87 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3">
         <v>1685200</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2024,8 +2192,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2043,93 +2213,101 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16927000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15962700</v>
+      </c>
+      <c r="F41" s="3">
         <v>20853300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>22325400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19975500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19962600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>26128500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>25032300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18473500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17984200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>43115900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>23058600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>606605200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>649427700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>587601300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>562948800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>527884800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
@@ -2137,93 +2315,105 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12760700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>12033700</v>
+      </c>
+      <c r="F43" s="3">
         <v>9125300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>9769500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>17260900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>17249700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>8753200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8386000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>16304300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>15872400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>12475500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>12065400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>935700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>882400</v>
+      </c>
+      <c r="F44" s="3">
         <v>664800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>711700</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>2460900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2357700</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
         <v>2377300</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
@@ -2231,46 +2421,52 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>96721500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>91211800</v>
+      </c>
+      <c r="F45" s="3">
         <v>12114900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>12970100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>65233100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>65191100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>10170900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9744200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>66268100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>64512800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>6479900</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2278,46 +2474,52 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127344800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>120090700</v>
+      </c>
+      <c r="F46" s="3">
         <v>649832900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>695707000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>102469400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>102403400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>635619300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>608952200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>101045900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>98369500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>592796000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3">
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
@@ -2325,149 +2527,173 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>606331000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>571791600</v>
+      </c>
+      <c r="F47" s="3">
         <v>14721400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>15760600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>538759200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>538412200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>13591000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>13020800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>504085600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>490733900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>10697000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>674327600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>447000</v>
+      </c>
+      <c r="F48" s="3">
         <v>494500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>529400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>539600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>539300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>551500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>528400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>460000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>447800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>392800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>11195300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>534300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>503900</v>
+      </c>
+      <c r="F49" s="3">
         <v>600900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>643300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>681200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>680700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>700600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>671200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>673500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>655700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>616900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>508000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2513,8 +2739,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2560,55 +2792,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13903300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13111300</v>
+      </c>
+      <c r="F52" s="3">
         <v>13321700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>14262200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>11707800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>11700200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>12359300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>11840700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>11725600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>11415000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>12195900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>6400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2654,55 +2898,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>763152500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>719679800</v>
+      </c>
+      <c r="F54" s="3">
         <v>681256200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>729348600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>665410000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>664981400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>665021400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>637120800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>635105700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>618283600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>618434800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>730100700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2720,8 +2976,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2739,46 +2997,48 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F57" s="3">
         <v>212800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>227900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>179500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>179300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>280200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>268500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>175400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>170700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>62700</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -2786,140 +3046,158 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>30659000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>28912500</v>
+      </c>
+      <c r="F58" s="3">
         <v>80349800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>86022000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>28049800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>28031800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>75735000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>72557500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>36023200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>35069000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>83805000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>43500</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>98817600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>93188500</v>
+      </c>
+      <c r="F59" s="3">
         <v>67299700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>72050700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>63322300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>63281500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>58429700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>55978300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>69859300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>68009000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>60159000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>622512400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>129486200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>122110100</v>
+      </c>
+      <c r="F60" s="3">
         <v>148609700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>159100700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>91551600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>91492600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>135092000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>129424300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>106057900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>103248700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>144649700</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3">
+        <v>0</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
@@ -2927,102 +3205,120 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6454300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6086600</v>
+      </c>
+      <c r="F61" s="3">
         <v>9712400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>10398100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7695200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7690300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7901100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7569600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7052900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6866100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6810000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7439700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>623886800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>588347400</v>
+      </c>
+      <c r="F62" s="3">
         <v>518273100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>554859900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>560976700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>560615300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>515743600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>494105900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>513570800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>499967800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>459300000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>264900</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3068,8 +3364,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3115,8 +3417,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3162,55 +3470,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>759827400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>716544100</v>
+      </c>
+      <c r="F66" s="3">
         <v>676860700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>724642800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>660463600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>660038100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>658927800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>631282800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>628684300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>612032400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>611768200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>717308400</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3228,8 +3548,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3275,8 +3597,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3322,8 +3650,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3357,11 +3691,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>3</v>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
       </c>
       <c r="P70" s="3" t="s">
         <v>3</v>
@@ -3369,8 +3703,14 @@
       <c r="Q70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3416,55 +3756,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>850800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>802300</v>
+      </c>
+      <c r="F72" s="3">
         <v>2145800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2297300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2650200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2648500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3786900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3628000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4084300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3976100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4466500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>10674500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3510,8 +3862,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3557,8 +3915,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3604,55 +3968,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3303200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3115000</v>
+      </c>
+      <c r="F76" s="3">
         <v>4441800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4755400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5002100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4998900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6147100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5889200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6465800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6294500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6701600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12792300</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3698,60 +4074,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3782,23 +4170,29 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3">
         <v>1685200</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3816,46 +4210,48 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>30600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>29300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>33700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>31200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>35900</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -3863,8 +4259,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3910,8 +4312,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3957,8 +4365,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4004,8 +4418,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4051,8 +4471,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4098,44 +4524,50 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-487100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-459300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-487000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-521400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2317800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2316300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3811100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>3651200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-12852800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-12512400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6926300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,8 +4577,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4164,55 +4602,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-41300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-44200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-18300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-18300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-42000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-40300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-108700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-105800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-76500</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4258,8 +4704,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4305,44 +4757,50 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="F94" s="3">
         <v>209100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>223800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-60000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-60000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-136900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-131200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-131500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-128000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-102400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4352,8 +4810,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4371,44 +4835,46 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>624700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>589200</v>
+      </c>
+      <c r="F96" s="3">
         <v>231600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>248000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>561100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>560800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>226100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>216600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>536900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>522700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>203600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -4418,8 +4884,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4465,8 +4937,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4512,8 +4990,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4559,44 +5043,50 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1803000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1700300</v>
+      </c>
+      <c r="F100" s="3">
         <v>800000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>856500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-598400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-598000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>137600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>131800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-490500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-477500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-204200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4606,44 +5096,50 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-25400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-24700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>13300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>12300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>42500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>46000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>10800</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4653,44 +5149,50 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2392800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2256500</v>
+      </c>
+      <c r="F102" s="3">
         <v>532700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>570300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2974300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2972400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3806000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3646300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-13500300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-13142700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6632900</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4698,6 +5200,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -656,82 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -768,23 +774,29 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>41481100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -821,23 +833,29 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>229100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,23 +892,29 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>41252100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -910,8 +934,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,8 +989,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1016,8 +1048,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1069,8 +1107,14 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1107,14 +1151,14 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1122,8 +1166,14 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1140,8 +1190,10 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1178,23 +1230,29 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3">
         <v>40000600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1231,23 +1289,29 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>1480500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1267,8 +1331,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1305,14 +1371,14 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1320,8 +1386,14 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1373,8 +1445,14 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1411,14 +1489,14 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1426,8 +1504,14 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1464,23 +1548,29 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1480500</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1517,23 +1607,29 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>166300</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1585,8 +1681,14 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1623,23 +1725,29 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1314200</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1676,23 +1784,29 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1338500</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1744,8 +1858,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1782,23 +1902,29 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3">
         <v>346800</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1850,8 +1976,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1903,8 +2035,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1941,14 +2079,14 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -1956,8 +2094,14 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1994,23 +2138,29 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1685200</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2062,8 +2212,14 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2100,81 +2256,93 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1685200</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2194,8 +2362,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2215,105 +2385,113 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23012100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>22983000</v>
+      </c>
+      <c r="F41" s="3">
         <v>16927000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15962700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>20853300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22325400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>19975500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>19962600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>26128500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>25032300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>18473500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>17984200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>43115900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>23058600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>688756400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>687886100</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>606605200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>649427700</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>587601300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>562948800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>527884800</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -2321,105 +2499,117 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6908500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6899700</v>
+      </c>
+      <c r="F43" s="3">
         <v>12760700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>12033700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>9125300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>9769500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>17260900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>17249700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8753200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8386000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>16304300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>15872400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>12475500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>12065400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>531600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>531000</v>
+      </c>
+      <c r="F44" s="3">
         <v>935700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>882400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>664800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>711700</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>2460900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2357700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3">
         <v>2377300</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
+      <c r="Q44" s="3">
+        <v>0</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
@@ -2427,52 +2617,58 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29686400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>29648900</v>
+      </c>
+      <c r="F45" s="3">
         <v>99241000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>93587800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>12114900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>12970100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>65233100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>65191100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10170900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>9744200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>66268100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>64512800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6479900</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2480,52 +2676,58 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>749413200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>748466300</v>
+      </c>
+      <c r="F46" s="3">
         <v>129864400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>122466700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>649832900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>695707000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>102469400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>102403400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>635619300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>608952200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>101045900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>98369500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>592796000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
+      <c r="Q46" s="3">
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
@@ -2533,167 +2735,191 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13916600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>13899000</v>
+      </c>
+      <c r="F47" s="3">
         <v>603811500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>569415600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>14721400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>15760600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>538759200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>538412200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>13591000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>13020800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>504085600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>490733900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>10697000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>674327600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>446800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>446300</v>
+      </c>
+      <c r="F48" s="3">
         <v>474000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>447000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>494500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>529400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>539600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>539300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>551500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>528400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>460000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>447800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>392800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>11195300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>531600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>531000</v>
+      </c>
+      <c r="F49" s="3">
         <v>534300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>503900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>600900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>643300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>681200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>680700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>700600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>671200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>673500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>655700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>616900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>508000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2745,8 +2971,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2798,61 +3030,73 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16965000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>16943600</v>
+      </c>
+      <c r="F52" s="3">
         <v>13903300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>13111300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13321700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>14262200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>11707800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>11700200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12359300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>11840700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>11725600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>11415000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>12195900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>6400</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2904,61 +3148,73 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>783671600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>782681400</v>
+      </c>
+      <c r="F54" s="3">
         <v>763152500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>719679800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>681256200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>729348600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>665410000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>664981400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>665021400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>637120800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>635105700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>618283600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>618434800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>730100700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2978,8 +3234,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2999,52 +3257,54 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F57" s="3">
         <v>9600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>212800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>227900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>179500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>179300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>280200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>268500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>175400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>170700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>62700</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3052,158 +3312,176 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>70510100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>70421000</v>
+      </c>
+      <c r="F58" s="3">
         <v>30659000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>28912500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>80349800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>86022000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>28049800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>28031800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>75735000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>72557500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>36023200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>35069000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>83805000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>43500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>98720100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>98595300</v>
+      </c>
+      <c r="F59" s="3">
         <v>98817600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>93188500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>67299700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>72050700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>63322300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>63281500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>58429700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>55978300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>69859300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>68009000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>60159000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>622512400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>169913900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>169699200</v>
+      </c>
+      <c r="F60" s="3">
         <v>129486200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>122110100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>148609700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>159100700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>91551600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>91492600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>135092000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>129424300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>106057900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>103248700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>144649700</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
+      <c r="Q60" s="3">
+        <v>0</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
@@ -3211,114 +3489,132 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6577400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6569100</v>
+      </c>
+      <c r="F61" s="3">
         <v>6454300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6086600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>9712400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10398100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7695200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7690300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7901100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7569600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7052900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6866100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6810000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7439700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>603935400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>603172300</v>
+      </c>
+      <c r="F62" s="3">
         <v>623886800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>588347400</v>
       </c>
-      <c r="F62" s="3">
-        <v>518273100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>554859900</v>
-      </c>
       <c r="H62" s="3">
+        <v>518276900</v>
+      </c>
+      <c r="I62" s="3">
+        <v>554864000</v>
+      </c>
+      <c r="J62" s="3">
         <v>560976700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>560615300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>515743600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>494105900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>513570800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>499967800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>459300000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>264900</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3370,8 +3666,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3423,8 +3725,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3476,61 +3784,73 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>780559900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>779573600</v>
+      </c>
+      <c r="F66" s="3">
         <v>759827400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>716544100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>676860700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>724642800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>660463600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>660038100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>658927800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>631282800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>628684300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>612032400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>611768200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>717308400</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3550,8 +3870,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3603,8 +3925,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3656,8 +3984,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3697,11 +4031,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q70" s="3" t="s">
-        <v>3</v>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
       </c>
       <c r="R70" s="3" t="s">
         <v>3</v>
@@ -3709,8 +4043,14 @@
       <c r="S70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3762,61 +4102,73 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>695800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>694900</v>
+      </c>
+      <c r="F72" s="3">
         <v>850800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>802300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2145800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2297300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2650200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2648500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3786900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3628000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4084300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3976100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4466500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>10674500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3868,8 +4220,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3921,8 +4279,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3974,61 +4338,73 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3072700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3068800</v>
+      </c>
+      <c r="F76" s="3">
         <v>3303200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3115000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4441800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4755400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5002100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4998900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6147100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5889200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6465800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6294500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6701600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>12792300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4080,66 +4456,78 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4176,23 +4564,29 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1685200</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4212,52 +4606,54 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>32800</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>30600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>29300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>33700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>31200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>35900</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4265,8 +4661,14 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4318,8 +4720,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4371,8 +4779,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4424,8 +4838,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4477,8 +4897,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4530,50 +4956,56 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3539000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3534600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-487100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-459300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-487000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-521400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2317800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2316300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3811100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3651200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-12852800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-12512400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>6926300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4583,8 +5015,14 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4604,61 +5042,69 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-21900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-20700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-41300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-44200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-18300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-18300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-42000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-40300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-108700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-105800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-76500</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4710,8 +5156,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4763,50 +5215,56 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>147200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-33600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-31700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>209100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>223800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-60000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-60000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-136900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-131200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-131500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-128000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-102400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4816,8 +5274,14 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4837,50 +5301,52 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>244000</v>
+      </c>
+      <c r="F96" s="3">
         <v>624700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>589200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>231600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>248000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>561100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>560800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>226100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>216600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>536900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>522700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>203600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -4890,8 +5356,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4943,8 +5415,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4996,8 +5474,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5049,50 +5533,56 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-199900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-199600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1803000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1700300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>800000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>856500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-598400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-598000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>137600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>131800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-490500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-477500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-204200</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5102,50 +5592,56 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F101" s="3">
         <v>1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-5700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-25400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-24700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>13300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>12300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>42500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>46000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>10800</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5155,50 +5651,56 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3481800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3477400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2392800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2256500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>532700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>570300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2974300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2972400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>3806000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3646300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-13500300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-13142700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>6632900</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5206,6 +5708,12 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
